--- a/prospects/83apps-prospects.xlsx
+++ b/prospects/83apps-prospects.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -522,47 +522,39 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Main Street Barber Shop</t>
+          <t>Next Level Pool Cleaning and Supplies</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>hairdresser</t>
+          <t>pool service</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Daytona Beach</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>+1-386-253-6249</t>
-        </is>
-      </c>
+          <t>Edgewater</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://mainstreetbarbershopdaytonabeach.com/</t>
+          <t>https://nextlevelpoolcleaning.com/</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Their domain now shows gambling spam: the old address lapsed or was taken over. Anyone who clicks it from Google Maps lands on spam.</t>
+          <t>Homepage returns a server error (HTTP 500, checked twice).</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Urgent and easy to show: "your web address is showing gambling ads". Offer a new site + a fresh domain, booking link.</t>
+          <t>Replacement site; weekly-service signup form.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>• Page is wider than a phone screen by 798px (sideways scrolling)
-• 91% of text is too small to read on a phone
-• No tap-to-call phone link anywhere
-• No "book / schedule / quote" button
-• No contact or request form on the homepage
-• Built on a dated template service (template vendor)</t>
+          <t>• Website is DOWN: homepage returns an error (500)
+• Check the business is still operating before reaching out</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -579,46 +571,39 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>HD Drain Cleaning</t>
+          <t>EverGreen Landscapes</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>plumber</t>
+          <t>lawn care / landscaping</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ormond Beach</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>+1-386-281-2523</t>
-        </is>
-      </c>
+          <t>Palm Coast</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://israelgalvan.com/</t>
+          <t>https://www.evergreenlandscapes.co/</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Their listed website redirects to an unrelated, broken site (israelgalvan.com).</t>
+          <t>Homepage returns "page not found" (404, checked twice).</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Plumber with no working site: every Google click is a lost emergency call. One-page site with tap-to-call.</t>
+          <t>Replacement site with a free-estimate form.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>• Page is wider than a phone screen by 83px (sideways scrolling)
-• No tap-to-call phone link anywhere
-• No booking/quote button on the first screen
-• Slowish: 7.3s to load
-• Built on a dated template service (WordPress, hibu)</t>
+          <t>• Website is DOWN: homepage returns an error (404)
+• Check the business is still operating before reaching out</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -635,38 +620,38 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Mid Florida Pool &amp; Spa</t>
+          <t>ReFine Pressure Washing and Exteriors</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>pool service</t>
+          <t>pressure washing</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>New Smyrna Beach</t>
+          <t>Palm Coast</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>http://midfloridapoolspa.com</t>
+          <t>https://refinepressurewashingandexteriors.com/</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Domain no longer exists (checked twice).</t>
+          <t>Homepage returns "page not found" (404, checked twice).</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Replacement site, fast; recurring-service quote form.</t>
+          <t>Replacement site; before/after gallery + quote form.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>• Website is DOWN: the web address no longer exists
+          <t>• Website is DOWN: homepage returns an error (404)
 • Check the business is still operating before reaching out</t>
         </is>
       </c>
@@ -684,183 +669,36 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Next Level Pool Cleaning and Supplies</t>
+          <t>Port Orange Car Doctor</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>pool service</t>
+          <t>auto repair</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Edgewater</t>
+          <t>Port Orange</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://nextlevelpoolcleaning.com/</t>
+          <t>https://haamacon.com/portorangecardoctor/</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Homepage returns a server error (HTTP 500, checked twice).</t>
+          <t>Their site is labeled "Unofficial Website" on someone else's domain (haamacon.com).</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Replacement site; weekly-service signup form.</t>
+          <t>They don't own their web presence. Offer an official site on their own domain.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>• Website is DOWN: homepage returns an error (500)
-• Check the business is still operating before reaching out</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>1 · Website down or hijacked</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>EverGreen Landscapes</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>lawn care / landscaping</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Palm Coast</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.evergreenlandscapes.co/</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Homepage returns "page not found" (404, checked twice).</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Replacement site with a free-estimate form.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>• Website is DOWN: homepage returns an error (404)
-• Check the business is still operating before reaching out</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>1 · Website down or hijacked</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ReFine Pressure Washing and Exteriors</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>pressure washing</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Palm Coast</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>https://refinepressurewashingandexteriors.com/</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Homepage returns "page not found" (404, checked twice).</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Replacement site; before/after gallery + quote form.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>• Website is DOWN: homepage returns an error (404)
-• Check the business is still operating before reaching out</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>1 · Website down or hijacked</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Port Orange Car Doctor</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>auto repair</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Port Orange</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>https://haamacon.com/portorangecardoctor/</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Their site is labeled "Unofficial Website" on someone else's domain (haamacon.com).</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>They don't own their web presence. Offer an official site on their own domain.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -870,50 +708,50 @@
 • Very little content</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>1 · Website down or hijacked</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>PawZazz Pet Salon</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>pet_grooming</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>South Daytona</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://pawzazzpetsalon.com/</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Site is still a "Launching Soon" placeholder, © 2021.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Finish what they started: simple site + online grooming booking.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>• No tap-to-call phone link anywhere
 • No "book / schedule / quote" button
@@ -924,107 +762,107 @@
 • Very little content</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>1 · Website down or hijacked</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Lee Nails</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>beauty</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Port Orange</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>+1 386 767 5006</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://lee-nails-lashes-llc.business.site/</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Their Google "business.site" page is dead (Google shut those down).</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Small, cheap site + booking link; many salons lost these sites the same way.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>• Website is DOWN: homepage returns an error (404)
 • Check the business is still operating before reaching out</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Fleur De Lis Salon</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>hairdresser</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Port Orange</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>+1-386-760-3515</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>http://www.fleurdelissaloninc.com/</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Desktop-only layout: on a phone the text is tiny and the page scrolls sideways.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Phone-vs-mockup side by side; add online booking.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • 50% of text is small on a phone
@@ -1037,50 +875,50 @@
 • No search description (basic SEO missing)</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Nord Pest Control</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>pest control</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Edgewater</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.nordpestcontrol.com/</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>No mobile layout; dated design.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Mobile rebuild with tap-to-call and a quote form.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -1089,50 +927,50 @@
 • Dated page code (table/font layout)</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Port Orange Pest Control</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>pest control</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Port Orange</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://portorangepest.com/</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>No mobile layout; dated design.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Mobile rebuild with tap-to-call and a quote form.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>• 67% of text is too small to read on a phone
 • No tap-to-call phone link anywhere
@@ -1143,50 +981,50 @@
 • No search description (basic SEO missing)</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Terry Blanks Jr DDS Family Dental Care</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>dentist</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>DeLand</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.terryblanksjrdds.com/</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Dated, not mobile-friendly.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>New-patient booking, insurance info up front, reminders later.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -1196,50 +1034,50 @@
 • Very little content</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Port Orange Pools</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>pool service</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>http://portorangepools.com/</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Old, not mobile-friendly (same operator as NSB Pools: one pitch covers both).</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>One modern site for both brands.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>• Page is wider than a phone screen by 21px (sideways scrolling)
 • 86% of text is too small to read on a phone
@@ -1249,50 +1087,50 @@
 • No search description (basic SEO missing)</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>NSB Pools</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>pool service</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>New Smyrna Beach</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>http://nsbpools.com/</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Old, not mobile-friendly (same operator as Port Orange Pools).</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Pitch together with Port Orange Pools.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>• 85% of text is too small to read on a phone
 • No "book / schedule / quote" button
@@ -1301,50 +1139,50 @@
 • No search description (basic SEO missing)</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Daytona Softwash</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>pressure washing</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://daytonasoftwash.com/</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Dated, hard to use on a phone.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Before/after gallery + instant quote form.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -1352,50 +1190,50 @@
 • No contact or request form on the homepage</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Ormond Lawn Care</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>lawn care / landscaping</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Ormond Beach</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.ormondlawncare.com/</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Dated, hard to use on a phone.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Mobile rebuild + quote form.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -1403,54 +1241,54 @@
 • No contact or request form on the homepage</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Natural Health and Wellness Chiropractic, LLC</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>massage</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>+1 386 872 7167</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.nhwchiro.com/</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Dated, not mobile-friendly.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Online booking + reminders.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No booking/quote button on the first screen
@@ -1458,104 +1296,104 @@
 • Copyright year 2019: looks unmaintained</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Dickinson &amp; McDonald, PA</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>CPA / tax preparer</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>DeLand</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.dickinsoncpa.com/</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Dated design, small text on phones.</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Clean professional refresh; client upload/intake form.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
 • Slowish: 8.8s to load</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Wholesale Furnature Outlet</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>furniture</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>+1-386-301-4969</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://wfoutlets.com/</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Dated, hard to use on a phone.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Mobile rebuild with inventory photos and tap-to-call.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • Tap-to-call not visible without scrolling
@@ -1566,54 +1404,54 @@
 • Very little content</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Consigned Interiors</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>furniture</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Palm Coast</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>+1 386 445 2301</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.consignedinteriors.com/</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Dated, hard to use on a phone.</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Mobile rebuild; "new arrivals" section they can update.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -1622,50 +1460,50 @@
 • Heavy page: 37.4 MB</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>On-Demand Handyman</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>handyman</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Ormond Beach</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.odhmfl.com/</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Works, but dated and weak on phones (moderate).</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Quote form + tap-to-call up top.</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • Tap-to-call not visible without scrolling
@@ -1674,50 +1512,50 @@
 • Uses Flash (dead technology)</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Pressure Clean USA</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>pressure washing</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.pressurecleanusa.com/</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Works, but dated (moderate).</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Refresh + quote form.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>• 100% of text is too small to read on a phone
 • No "book / schedule / quote" button
@@ -1726,50 +1564,50 @@
 • No search description (basic SEO missing)</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Bulldog Lawn &amp; Landscaping</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>lawn care / landscaping</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Port Orange</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.bulldoglawnandlandscaping.com/</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Works, but dated (moderate).</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Refresh + quote form.</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -1778,50 +1616,50 @@
 • Heavy page: 25.2 MB</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>All Pools Matter LLC</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>pool service</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Edgewater</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.allpoolsmatter.com/</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Works, but dated (moderate).</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Refresh + service signup form.</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • Tap-to-call not visible without scrolling
@@ -1831,50 +1669,50 @@
 • Very little content</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>3 · Free builder web address</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Lightyear Electric LLC</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>electrician</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>New Smyrna Beach</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://lightyearelectricl.wixsite.com/my-site</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Site is on a free Wix address (lightyearelectricl.wixsite.com/my-site).</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Own domain + proper site; low price, fast win.</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>• Runs on a free builder subdomain, not its own web address
 • Not built for phones (no mobile layout)
@@ -1883,50 +1721,50 @@
 • Very little content</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>3 · Free builder web address</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>R.J.P Handyman LLC</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>handyman</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>New Smyrna Beach</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://rjpcmp.wixsite.com/rjphandymanllc</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Site is on a free Wix address (rjpcmp.wixsite.com).</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Own domain + proper site; low price, fast win.</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>• Runs on a free builder subdomain, not its own web address
 • Not built for phones (no mobile layout)
@@ -1934,100 +1772,100 @@
 • No contact or request form on the homepage</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>3 · Free builder web address</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>G &amp; M Automotive Center Inc</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>auto repair</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Port Orange</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://g-inc-port-orange.edan.io/</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Site is on a free builder address (g-inc-port-orange.edan.io).</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Own domain + proper site.</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>• Runs on a free builder subdomain, not its own web address
 • No "book / schedule / quote" button
 • No contact or request form on the homepage</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>3 · Free builder web address</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>All of the Above Handyman Solutions LLC</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>handyman</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://aotahs.jobbersites.com/</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Decent-looking page, but on a Jobber subdomain (aotahs.jobbersites.com).</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Own domain + SEO; lighter pitch.</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>• Runs on a free builder subdomain, not its own web address
 • Tap-to-call not visible without scrolling
@@ -2035,8 +1873,8 @@
 • No contact or request form on the homepage</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2310,7 +2148,7 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>1 · Website down or hijacked</t>
+          <t>Checked: not a prospect (Listed as CLOSED on Yelp)</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr"/>
@@ -3352,7 +3190,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1 · Website down or hijacked</t>
+          <t>Checked: not a prospect (Moved to daytonabarbershop.com, which works well (old address now shows spam))</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5303,7 +5141,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1 · Website down or hijacked</t>
+          <t>Checked: not a prospect (Moved to daytonadraincleaning.com, which works well (old address now shows spam))</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">

--- a/prospects/83apps-prospects.xlsx
+++ b/prospects/83apps-prospects.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Homepage returns a server error (HTTP 500, checked twice).</t>
+          <t>The site shows a WordPress "critical error" (HTTP 500), and their BBB and Facebook pages still link to it.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Homepage returns "page not found" (404, checked twice).</t>
+          <t>Their host says the site is not published. No other site found. Yelp has one listing marked closed and another active, so call first.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -620,85 +620,36 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ReFine Pressure Washing and Exteriors</t>
+          <t>Port Orange Car Doctor</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>pressure washing</t>
+          <t>auto repair</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Palm Coast</t>
+          <t>Port Orange</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://refinepressurewashingandexteriors.com/</t>
+          <t>https://haamacon.com/portorangecardoctor/</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Homepage returns "page not found" (404, checked twice).</t>
+          <t>Their site is labeled "Unofficial Website" on someone else's domain (haamacon.com).</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Replacement site; before/after gallery + quote form.</t>
+          <t>They don't own their web presence. Offer an official site on their own domain.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>• Website is DOWN: homepage returns an error (404)
-• Check the business is still operating before reaching out</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1 · Website down or hijacked</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Port Orange Car Doctor</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>auto repair</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Port Orange</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>https://haamacon.com/portorangecardoctor/</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Their site is labeled "Unofficial Website" on someone else's domain (haamacon.com).</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>They don't own their web presence. Offer an official site on their own domain.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -708,50 +659,50 @@
 • Very little content</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>1 · Website down or hijacked</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>PawZazz Pet Salon</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>pet_grooming</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>South Daytona</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://pawzazzpetsalon.com/</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Site is still a "Launching Soon" placeholder, © 2021.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Finish what they started: simple site + online grooming booking.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>• No tap-to-call phone link anywhere
 • No "book / schedule / quote" button
@@ -762,6 +713,59 @@
 • Very little content</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1 · Website down or hijacked</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Lee Nails</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>beauty</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Port Orange</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>+1 386 767 5006</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://lee-nails-lashes-llc.business.site/</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Their Google "business.site" page is dead (Google shut those down). All that is left is Facebook and a salon-software booking page.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Small, cheap site + booking link; many salons lost these sites the same way.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>• Website is DOWN: homepage returns an error (404)
+• Check the business is still operating before reaching out</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
     </row>
@@ -771,154 +775,41 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>1 · Website down or hijacked</t>
+          <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Lee Nails</t>
+          <t>Nord Pest Control</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>beauty</t>
+          <t>pest control</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Port Orange</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>+1 386 767 5006</t>
-        </is>
-      </c>
+          <t>Edgewater</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://lee-nails-lashes-llc.business.site/</t>
+          <t>https://www.nordpestcontrol.com/</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Their Google "business.site" page is dead (Google shut those down).</t>
+          <t>No mobile layout; dated design.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Small, cheap site + booking link; many salons lost these sites the same way.</t>
+          <t>Mobile rebuild with tap-to-call and a quote form.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>• Website is DOWN: homepage returns an error (404)
-• Check the business is still operating before reaching out</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2 · Not built for phones / clearly dated</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Fleur De Lis Salon</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>hairdresser</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Port Orange</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>+1-386-760-3515</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>http://www.fleurdelissaloninc.com/</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Desktop-only layout: on a phone the text is tiny and the page scrolls sideways.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Phone-vs-mockup side by side; add online booking.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>• Not built for phones (no mobile layout)
-• 50% of text is small on a phone
-• No tap-to-call phone link anywhere
-• No "book / schedule / quote" button
-• No contact or request form on the homepage
-• Not secure: browsers show "Not secure" (no https)
-• Dated page code (table/font layout)
-• Built on a dated template service (Homestead)
-• No search description (basic SEO missing)</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2 · Not built for phones / clearly dated</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nord Pest Control</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>pest control</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Edgewater</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nordpestcontrol.com/</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>No mobile layout; dated design.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Mobile rebuild with tap-to-call and a quote form.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -927,50 +818,50 @@
 • Dated page code (table/font layout)</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Port Orange Pest Control</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>pest control</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Port Orange</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://portorangepest.com/</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>No mobile layout; dated design.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Mobile rebuild with tap-to-call and a quote form.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>• 67% of text is too small to read on a phone
 • No tap-to-call phone link anywhere
@@ -981,50 +872,50 @@
 • No search description (basic SEO missing)</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Terry Blanks Jr DDS Family Dental Care</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>dentist</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>DeLand</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.terryblanksjrdds.com/</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Dated, not mobile-friendly.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>New-patient booking, insurance info up front, reminders later.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -1034,50 +925,50 @@
 • Very little content</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Port Orange Pools</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>pool service</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>http://portorangepools.com/</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Old, not mobile-friendly (same operator as NSB Pools: one pitch covers both).</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>One modern site for both brands.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>• Page is wider than a phone screen by 21px (sideways scrolling)
 • 86% of text is too small to read on a phone
@@ -1087,50 +978,50 @@
 • No search description (basic SEO missing)</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>NSB Pools</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>pool service</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>New Smyrna Beach</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>http://nsbpools.com/</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Old, not mobile-friendly (same operator as Port Orange Pools).</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Pitch together with Port Orange Pools.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>• 85% of text is too small to read on a phone
 • No "book / schedule / quote" button
@@ -1139,50 +1030,50 @@
 • No search description (basic SEO missing)</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Daytona Softwash</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>pressure washing</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://daytonasoftwash.com/</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Dated, hard to use on a phone.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Before/after gallery + instant quote form.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -1190,50 +1081,50 @@
 • No contact or request form on the homepage</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Ormond Lawn Care</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>lawn care / landscaping</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Ormond Beach</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.ormondlawncare.com/</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Dated, hard to use on a phone.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Mobile rebuild + quote form.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -1241,54 +1132,54 @@
 • No contact or request form on the homepage</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Natural Health and Wellness Chiropractic, LLC</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>massage</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>+1 386 872 7167</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.nhwchiro.com/</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Dated, not mobile-friendly.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Online booking + reminders.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No booking/quote button on the first screen
@@ -1296,104 +1187,104 @@
 • Copyright year 2019: looks unmaintained</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Dickinson &amp; McDonald, PA</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>CPA / tax preparer</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>DeLand</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.dickinsoncpa.com/</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Dated design, small text on phones.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Clean professional refresh; client upload/intake form.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
 • Slowish: 8.8s to load</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Wholesale Furnature Outlet</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>furniture</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>+1-386-301-4969</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://wfoutlets.com/</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Dated, hard to use on a phone.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Mobile rebuild with inventory photos and tap-to-call.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • Tap-to-call not visible without scrolling
@@ -1404,54 +1295,54 @@
 • Very little content</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Consigned Interiors</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>furniture</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Palm Coast</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>+1 386 445 2301</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.consignedinteriors.com/</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Dated, hard to use on a phone.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Mobile rebuild; "new arrivals" section they can update.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -1460,50 +1351,50 @@
 • Heavy page: 37.4 MB</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>On-Demand Handyman</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>handyman</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Ormond Beach</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.odhmfl.com/</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Works, but dated and weak on phones (moderate).</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Quote form + tap-to-call up top.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • Tap-to-call not visible without scrolling
@@ -1512,50 +1403,50 @@
 • Uses Flash (dead technology)</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Pressure Clean USA</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>pressure washing</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.pressurecleanusa.com/</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Works, but dated (moderate).</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Refresh + quote form.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>• 100% of text is too small to read on a phone
 • No "book / schedule / quote" button
@@ -1564,50 +1455,50 @@
 • No search description (basic SEO missing)</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Bulldog Lawn &amp; Landscaping</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>lawn care / landscaping</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Port Orange</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.bulldoglawnandlandscaping.com/</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Works, but dated (moderate).</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Refresh + quote form.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • No tap-to-call phone link anywhere
@@ -1616,50 +1507,50 @@
 • Heavy page: 25.2 MB</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>2 · Not built for phones / clearly dated</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>All Pools Matter LLC</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>pool service</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Edgewater</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.allpoolsmatter.com/</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Works, but dated (moderate).</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Refresh + service signup form.</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>• Not built for phones (no mobile layout)
 • Tap-to-call not visible without scrolling
@@ -1669,50 +1560,50 @@
 • Very little content</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>3 · Free builder web address</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Lightyear Electric LLC</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>electrician</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>New Smyrna Beach</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://lightyearelectricl.wixsite.com/my-site</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Site is on a free Wix address (lightyearelectricl.wixsite.com/my-site).</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Own domain + proper site; low price, fast win.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>• Runs on a free builder subdomain, not its own web address
 • Not built for phones (no mobile layout)
@@ -1721,50 +1612,50 @@
 • Very little content</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>3 · Free builder web address</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>R.J.P Handyman LLC</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>handyman</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>New Smyrna Beach</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://rjpcmp.wixsite.com/rjphandymanllc</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Site is on a free Wix address (rjpcmp.wixsite.com).</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Own domain + proper site; low price, fast win.</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>• Runs on a free builder subdomain, not its own web address
 • Not built for phones (no mobile layout)
@@ -1772,100 +1663,100 @@
 • No contact or request form on the homepage</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>3 · Free builder web address</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>G &amp; M Automotive Center Inc</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>auto repair</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Port Orange</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://g-inc-port-orange.edan.io/</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Site is on a free builder address (g-inc-port-orange.edan.io).</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Own domain + proper site.</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>• Runs on a free builder subdomain, not its own web address
 • No "book / schedule / quote" button
 • No contact or request form on the homepage</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>3 · Free builder web address</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>All of the Above Handyman Solutions LLC</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>handyman</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Daytona Beach</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://aotahs.jobbersites.com/</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Decent-looking page, but on a Jobber subdomain (aotahs.jobbersites.com).</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Own domain + SEO; lighter pitch.</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>• Runs on a free builder subdomain, not its own web address
 • Tap-to-call not visible without scrolling
@@ -1873,8 +1764,8 @@
 • No contact or request form on the homepage</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2075,7 +1966,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2 · Not built for phones / clearly dated</t>
+          <t>Checked: not a prospect (Moved to fdlsalon.com, which is modern and mobile-friendly (the old site still loads))</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -2369,7 +2260,7 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1 · Website down or hijacked</t>
+          <t>Checked: not a prospect (Rebranded as Top Elite Properties (topeliteproperties.com), which is modern)</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr"/>
